--- a/Result/profitability/6143.xlsx
+++ b/Result/profitability/6143.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>1.46125</v>
+        <v>1.49625</v>
       </c>
       <c r="N2" t="n">
-        <v>21.6925</v>
+        <v>21.5675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.36625</v>
+        <v>1.28</v>
       </c>
       <c r="N3" t="n">
-        <v>21.45</v>
+        <v>21.48875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15625</v>
+        <v>1.2125</v>
       </c>
       <c r="N4" t="n">
-        <v>21.285</v>
+        <v>21.05875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0725</v>
+        <v>1.21875</v>
       </c>
       <c r="N5" t="n">
-        <v>20.9175</v>
+        <v>20.89625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09125</v>
+        <v>1.03125</v>
       </c>
       <c r="N6" t="n">
-        <v>21.415</v>
+        <v>21.1175</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9212500000000001</v>
+        <v>0.78125</v>
       </c>
       <c r="N7" t="n">
-        <v>21.92375</v>
+        <v>21.67375</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7150000000000001</v>
+        <v>0.7412500000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>22.2725</v>
+        <v>22.1325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6143</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2310</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1834</v>
+      </c>
+      <c r="E75" t="n">
+        <v>476</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>248</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.75%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>261</v>
+      </c>
+      <c r="K75" t="n">
+        <v>139</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.64125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2100000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1489361702127661</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.119999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05151793928242854</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1699999999999982</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.00817700817700806</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
